--- a/module-4-excel-statistics/excel/workbook1.xlsx
+++ b/module-4-excel-statistics/excel/workbook1.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analitics-5-30to7-00\module-4-excel-statistics\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE8BB4E-9C51-4A69-9ECA-0D821E8FF372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C5AD6C-74C0-48AA-8643-C06E93E71A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F67F7B41-BC77-4604-9200-C18108E4C2E6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F67F7B41-BC77-4604-9200-C18108E4C2E6}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="employe_data" sheetId="1" r:id="rId1"/>
+    <sheet name="cetegory" sheetId="2" r:id="rId2"/>
+    <sheet name="attendance" sheetId="3" r:id="rId3"/>
+    <sheet name="data_set" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t xml:space="preserve">Name </t>
   </si>
@@ -63,6 +66,12 @@
   </si>
   <si>
     <t>Krish</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Age</t>
   </si>
 </sst>
 </file>
@@ -510,4 +519,102 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{150441D8-015E-4769-A20D-4601C53664B8}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>15500</v>
+      </c>
+      <c r="C2">
+        <v>35</v>
+      </c>
+      <c r="D2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>12500</v>
+      </c>
+      <c r="C3">
+        <v>32</v>
+      </c>
+      <c r="D3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>11500</v>
+      </c>
+      <c r="C4">
+        <v>30</v>
+      </c>
+      <c r="D4">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>10500</v>
+      </c>
+      <c r="C5">
+        <v>22</v>
+      </c>
+      <c r="D5">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67813E43-62EE-4A7E-BABB-D2CB8CF2F676}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D247C01-4478-4643-B13F-127FF8FE22EE}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>